--- a/models/demo-ipcc-tier1/FAOSTAT_data_en_1-20-2026.xlsx
+++ b/models/demo-ipcc-tier1/FAOSTAT_data_en_1-20-2026.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/ipcc-tier1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-ipcc-tier1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00F1F723-FFEF-8149-8E8F-F2705B3D2FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789AE349-6DFF-164B-B859-D0CC0AEBED0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="26980" xr2:uid="{B6588F08-F6F7-9F4B-8806-3701B203176D}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="26880" xr2:uid="{B6588F08-F6F7-9F4B-8806-3701B203176D}"/>
   </bookViews>
   <sheets>
     <sheet name="FAOSTAT_data_en_1-20-2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -612,22 +612,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>153121</xdr:rowOff>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>188054</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED39AEB1-2013-8B10-2F56-7EE48836C19B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9648BA2-AA2E-D68F-D205-BFFD67636011}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -643,8 +643,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10972800" y="8420100"/>
-          <a:ext cx="7772400" cy="7176221"/>
+          <a:off x="12852400" y="190500"/>
+          <a:ext cx="7670800" cy="12799154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -656,22 +656,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>762148</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
+      <xdr:colOff>781271</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40E98030-D78C-FC3B-FA5A-B9503605B170}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B939232-8ADC-3903-15BB-8C339036D67D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -679,16 +679,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect t="1776"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10972800" y="0"/>
-          <a:ext cx="7772400" cy="8435340"/>
+          <a:off x="12852548" y="13119099"/>
+          <a:ext cx="7639123" cy="7594601"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
